--- a/agile/Wordle_Duel_Product_Backlog.xlsx
+++ b/agile/Wordle_Duel_Product_Backlog.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/81ab7734a6a69e1a/Documents/Cna/Fall 2025/CP3490 Software Engineering/Wordle_Duel/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/81ab7734a6a69e1a/Documents/Cna/Fall 2025/CP3490 Software Engineering/Wordle_Duel/agile/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="8_{0851C2B4-1840-4623-96D0-A3D921CC4092}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{937B1292-DF62-4BDC-B3E8-06EF371D5525}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="8_{0851C2B4-1840-4623-96D0-A3D921CC4092}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C32D9747-3A39-4586-B1EF-A0665B10437A}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="28">
   <si>
     <t>ID</t>
   </si>
@@ -47,9 +47,6 @@
   </si>
   <si>
     <t>Matchmaking pairs two players in under 2 seconds.</t>
-  </si>
-  <si>
-    <t>To Do</t>
   </si>
   <si>
     <t>As a player, I want to take turns submitting six-letter word guesses so the game is fair and turn-based.</t>
@@ -522,7 +519,7 @@
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -530,7 +527,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C3" t="s">
         <v>7</v>
@@ -539,10 +536,10 @@
         <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -550,7 +547,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C4" t="s">
         <v>7</v>
@@ -559,10 +556,10 @@
         <v>5</v>
       </c>
       <c r="E4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -570,19 +567,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" t="s">
         <v>14</v>
-      </c>
-      <c r="C5" t="s">
-        <v>15</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -590,7 +587,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
         <v>7</v>
@@ -599,10 +596,10 @@
         <v>4</v>
       </c>
       <c r="E6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -610,19 +607,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D7">
         <v>3</v>
       </c>
       <c r="E7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -630,7 +627,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C8" t="s">
         <v>7</v>
@@ -639,10 +636,10 @@
         <v>5</v>
       </c>
       <c r="E8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -650,19 +647,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D9">
         <v>2</v>
       </c>
       <c r="E9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -670,19 +667,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D10">
         <v>3</v>
       </c>
       <c r="E10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F10" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
